--- a/nr-update-termino/ig/ValueSet-method-glucose-vs.xlsx
+++ b/nr-update-termino/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T09:32:52+00:00</t>
+    <t>2025-07-21T12:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-termino/ig/ValueSet-method-glucose-vs.xlsx
+++ b/nr-update-termino/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:02:52+00:00</t>
+    <t>2025-07-21T12:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
